--- a/data/2026/cjsl/fall/sc-gjoa-king.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-king.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>
@@ -229,7 +229,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>16:00 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -249,7 +249,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Randall's Island - 72</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -257,7 +257,11 @@
           <t>U11 (9v9) - D4 City</t>
         </is>
       </c>
-      <c r="I4" s="0"/>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">

--- a/data/2026/cjsl/fall/sc-gjoa-king.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-king.xlsx
@@ -234,12 +234,12 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Soccer Stars United Pulsar 2015/2016</t>
+          <t>Soccer Stars United Met Oval - SSU Black 2015/2016 (Formerly Pulsar)</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>Soccer Stars United Pulsar 2015/2016</t>
+          <t>Soccer Stars United Met Oval - SSU Black 2015/2016 (Formerly Pulsar)</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/sc-gjoa-king.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-king.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="50.6"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="49.50000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>15:00 EDT</t>
+          <t>16:00 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa King</t>
+          <t>Soccer Stars United Met Oval - SSU Black 2015/2016 (Formerly Pulsar)</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 2</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Islas Malvinas Int. IMIFC 2016/2017</t>
+          <t>SC Gjoa King</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field A Small Sided  - A</t>
+          <t>Randall's Island - 72</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>16:00 EDT</t>
+          <t>10:30 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Soccer Stars United Met Oval - SSU Black 2015/2016 (Formerly Pulsar)</t>
+          <t>SC Gjoa King</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>7 - 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa King</t>
+          <t>NY Kids S.C. 2015/16 boys</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 72</t>
+          <t>Dyker Turf Field B Small Sided  - B</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -259,22 +259,22 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Sunday, October 25, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10:30 EDT</t>
+          <t>13:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>NY Kids S.C. 2015/16 boys</t>
+          <t>Islas Malvinas Int. IMIFC 2016/2017</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field B Small Sided  - B</t>
+          <t>Dyker Turf Field A Small Sided  - A</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/sc-gjoa-king.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-king.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 3</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
